--- a/MAJSushiConfig/ig/StructureDefinition-fr-device-auteur-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-device-auteur-document.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-device-auteur-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-device-auteur-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1069,7 +1069,7 @@
     <t>Device.owner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-organization-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-organization-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1491,7 +1491,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="94.7109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="91.51171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
